--- a/Backend/public/docs/paquetes-format.xlsx
+++ b/Backend/public/docs/paquetes-format.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jesus Alvarado\Documents\GitHub\Smartyme\Backend\public\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jesus Alvarado\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAF7D86-4E20-4047-9003-1F9B10664411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06B73AE-F255-48E6-9C77-731CF88E3B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>guia</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>otros</t>
+  </si>
+  <si>
+    <t>seguimiento</t>
   </si>
 </sst>
 </file>
@@ -389,15 +392,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D6F6C4F-5681-42C3-A988-6FDFD305B6BC}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="8" max="9" width="18.88671875" customWidth="1"/>
+    <col min="2" max="3" width="17.5546875" customWidth="1"/>
+    <col min="9" max="10" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -405,30 +408,33 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
     </row>
